--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_hoog.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_hoog.xlsx
@@ -430,7 +430,7 @@
         <v>2153</v>
       </c>
       <c r="C2">
-        <v>2020</v>
+        <v>2044</v>
       </c>
       <c r="D2">
         <v>1289</v>
@@ -442,7 +442,7 @@
         <v>2167</v>
       </c>
       <c r="G2">
-        <v>2118</v>
+        <v>2137</v>
       </c>
       <c r="H2">
         <v>2208</v>
@@ -456,7 +456,7 @@
         <v>2168</v>
       </c>
       <c r="C3">
-        <v>2006</v>
+        <v>2077</v>
       </c>
       <c r="D3">
         <v>1199</v>
@@ -468,7 +468,7 @@
         <v>2178</v>
       </c>
       <c r="G3">
-        <v>2121</v>
+        <v>2149</v>
       </c>
       <c r="H3">
         <v>2210</v>
@@ -482,7 +482,7 @@
         <v>2126</v>
       </c>
       <c r="C4">
-        <v>2000</v>
+        <v>2072</v>
       </c>
       <c r="D4">
         <v>1332</v>
@@ -494,7 +494,7 @@
         <v>2153</v>
       </c>
       <c r="G4">
-        <v>2129</v>
+        <v>2158</v>
       </c>
       <c r="H4">
         <v>2206</v>
@@ -508,7 +508,7 @@
         <v>2181</v>
       </c>
       <c r="C5">
-        <v>2002</v>
+        <v>2073</v>
       </c>
       <c r="D5">
         <v>1382</v>
@@ -520,7 +520,7 @@
         <v>2185</v>
       </c>
       <c r="G5">
-        <v>2127</v>
+        <v>2139</v>
       </c>
       <c r="H5">
         <v>2206</v>
@@ -534,7 +534,7 @@
         <v>2185</v>
       </c>
       <c r="C6">
-        <v>2010</v>
+        <v>2093</v>
       </c>
       <c r="D6">
         <v>475</v>
@@ -546,7 +546,7 @@
         <v>2189</v>
       </c>
       <c r="G6">
-        <v>2047</v>
+        <v>2114</v>
       </c>
       <c r="H6">
         <v>2216</v>
@@ -560,7 +560,7 @@
         <v>2176</v>
       </c>
       <c r="C7">
-        <v>2003</v>
+        <v>2073</v>
       </c>
       <c r="D7">
         <v>738</v>
@@ -572,7 +572,7 @@
         <v>2180</v>
       </c>
       <c r="G7">
-        <v>2056</v>
+        <v>2105</v>
       </c>
       <c r="H7">
         <v>2208</v>
@@ -586,7 +586,7 @@
         <v>2171</v>
       </c>
       <c r="C8">
-        <v>2005</v>
+        <v>2087</v>
       </c>
       <c r="D8">
         <v>805</v>
@@ -598,7 +598,7 @@
         <v>2177</v>
       </c>
       <c r="G8">
-        <v>2072</v>
+        <v>2124</v>
       </c>
       <c r="H8">
         <v>2215</v>
@@ -612,7 +612,7 @@
         <v>2169</v>
       </c>
       <c r="C9">
-        <v>1996</v>
+        <v>2065</v>
       </c>
       <c r="D9">
         <v>682</v>
@@ -624,7 +624,7 @@
         <v>2174</v>
       </c>
       <c r="G9">
-        <v>2050</v>
+        <v>2097</v>
       </c>
       <c r="H9">
         <v>2201</v>
@@ -638,22 +638,22 @@
         <v>1949</v>
       </c>
       <c r="C10">
-        <v>2008</v>
+        <v>2020</v>
       </c>
       <c r="D10">
         <v>1398</v>
       </c>
       <c r="E10">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="F10">
         <v>2014</v>
       </c>
       <c r="G10">
-        <v>2078</v>
+        <v>2086</v>
       </c>
       <c r="H10">
-        <v>2157</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="11" spans="1:12">
@@ -664,22 +664,22 @@
         <v>1895</v>
       </c>
       <c r="C11">
-        <v>2025</v>
+        <v>2039</v>
       </c>
       <c r="D11">
         <v>1220</v>
       </c>
       <c r="E11">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="F11">
         <v>1954</v>
       </c>
       <c r="G11">
-        <v>2074</v>
+        <v>2080</v>
       </c>
       <c r="H11">
-        <v>2162</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -690,22 +690,22 @@
         <v>1520</v>
       </c>
       <c r="C12">
-        <v>1984</v>
+        <v>1993</v>
       </c>
       <c r="D12">
         <v>604</v>
       </c>
       <c r="E12">
-        <v>2096</v>
+        <v>2099</v>
       </c>
       <c r="F12">
         <v>1578</v>
       </c>
       <c r="G12">
-        <v>2000</v>
+        <v>2009</v>
       </c>
       <c r="H12">
-        <v>2097</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="13" spans="1:12">
@@ -716,22 +716,22 @@
         <v>1896</v>
       </c>
       <c r="C13">
-        <v>2000</v>
+        <v>2012</v>
       </c>
       <c r="D13">
         <v>1193</v>
       </c>
       <c r="E13">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="F13">
         <v>1952</v>
       </c>
       <c r="G13">
-        <v>2049</v>
+        <v>2057</v>
       </c>
       <c r="H13">
-        <v>2145</v>
+        <v>2147</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_hoog.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/alle groepen/herkomsten/restdag/Pot_totaal_hoog.xlsx
@@ -14,15 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Zone</t>
   </si>
   <si>
     <t>Fiets</t>
-  </si>
-  <si>
-    <t>EFiets</t>
   </si>
   <si>
     <t>Auto</t>
@@ -37,19 +34,10 @@
     <t>OV_Fiets</t>
   </si>
   <si>
-    <t>Auto_EFiets</t>
-  </si>
-  <si>
-    <t>OV_EFiets</t>
-  </si>
-  <si>
     <t>Auto_OV</t>
   </si>
   <si>
     <t>Auto_OV_Fiets</t>
-  </si>
-  <si>
-    <t>Auto_OV_EFiets</t>
   </si>
 </sst>
 </file>
@@ -381,10 +369,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -409,20 +397,8 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>1</v>
       </c>
@@ -448,7 +424,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>2</v>
       </c>
@@ -474,7 +450,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>3</v>
       </c>
@@ -500,7 +476,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>4</v>
       </c>
@@ -526,7 +502,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>5</v>
       </c>
@@ -552,7 +528,7 @@
         <v>2216</v>
       </c>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>6</v>
       </c>
@@ -578,7 +554,7 @@
         <v>2208</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>7</v>
       </c>
@@ -604,7 +580,7 @@
         <v>2215</v>
       </c>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>8</v>
       </c>
@@ -630,7 +606,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>9</v>
       </c>
@@ -656,7 +632,7 @@
         <v>2159</v>
       </c>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>10</v>
       </c>
@@ -682,7 +658,7 @@
         <v>2163</v>
       </c>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>11</v>
       </c>
@@ -708,7 +684,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>12</v>
       </c>
